--- a/data/TC_QuizManagement.xlsx
+++ b/data/TC_QuizManagement.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC_QuizCRUD" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TC_QuizCRUD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,12 @@
       <color rgb="00276221"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -103,8 +107,13 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -170,11 +179,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BDBDBD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDBDBD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,6 +220,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -563,8 +589,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -771,14 +797,48 @@
           <t>Delete quiz doc via Firestore API</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:20</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -821,14 +881,44 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
       <c r="J7" s="8" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:21</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -871,14 +961,44 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:21</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -921,14 +1041,44 @@
           <t>Delete quiz doc</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
       <c r="J9" s="8" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:21</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -971,14 +1121,44 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1021,14 +1201,44 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
       <c r="J11" s="8" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1071,16 +1281,24 @@
           <t>Restore original title via Firestore API</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>TC-CQ-001 chưa tạo quiz – skip</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>Bug: edit not persisted</t>
+          <t>Bug: edit not persisted | Run: 2026-04-18 12:22</t>
         </is>
       </c>
     </row>
@@ -1125,14 +1343,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Không có quiz ID để test</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr"/>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1175,14 +1405,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Không có quiz ID để test</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr"/>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1225,16 +1467,24 @@
           <t>Re-create quiz for cleanup</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Không có quiz ID</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>Bug: delete partially works</t>
+          <t>Bug: delete partially works | Run: 2026-04-18 12:22</t>
         </is>
       </c>
     </row>
@@ -1279,14 +1529,26 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Không có quiz ID</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr"/>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1329,16 +1591,24 @@
           <t>Delete imported questions</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>File not found: C:\quiz-trivia-tooltest\data\sample_import_valid.csv</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>Known: import fails for most formats</t>
+          <t>Known: import fails for most formats | Run: 2026-04-18 12:22</t>
         </is>
       </c>
     </row>
@@ -1383,14 +1653,44 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="inlineStr"/>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1433,14 +1733,44 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
       <c r="J19" s="8" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1483,14 +1813,44 @@
           <t>None</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
       <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:23</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1533,16 +1893,24 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Không có quiz ID</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>Verified in system test</t>
+          <t>Verified in system test | Run: 2026-04-18 12:23</t>
         </is>
       </c>
     </row>
@@ -1587,16 +1955,24 @@
           <t>Reset status to draft</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Không có quiz ID</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>Bug: state transition unreliable</t>
+          <t>Bug: state transition unreliable | Run: 2026-04-18 12:23</t>
         </is>
       </c>
     </row>
@@ -1641,16 +2017,24 @@
           <t>Set back to pending</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr"/>
-      <c r="J23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Không có quiz ID</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>Bug: approval flow broken</t>
+          <t>Bug: approval flow broken | Run: 2026-04-18 12:23</t>
         </is>
       </c>
     </row>
@@ -1695,16 +2079,24 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="6" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Không có quiz ID</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>Bug: client-side only check</t>
+          <t>Bug: client-side only check | Run: 2026-04-18 12:23</t>
         </is>
       </c>
     </row>
@@ -1749,16 +2141,532 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Không có quiz ID</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>Verified in system test</t>
+          <t>Verified in system test | Run: 2026-04-18 12:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>TC-CQ-005</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Create Quiz - Duration</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Duration = -1 (so am) phai bi tu choi</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>CREATOR</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = -1</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Hien thi loi: 'Thoi gian phai tu 5 den 120 phut'; button Next bi disabled</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Khong co document nao duoc tao trong Firestore</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>BVA: gia tri am – ngoai vung hop le | Run: 2026-04-18 12:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="55" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>TC-CQ-006</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Create Quiz - Duration</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Duration = 4 (bien duoi - 1) phai bi tu choi</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>CREATOR</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 4</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Hien thi loi hoac button Next bi disabled; khong chuyen buoc</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Khong co document nao duoc tao trong Firestore</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>BVA: bien duoi - 1 = 4 (invalid) | Run: 2026-04-18 12:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="55" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>TC-CQ-007</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Create Quiz - Duration</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Duration = 5 (bien duoi) phai duoc chap nhan</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>CREATOR</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 5</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Chuyen sang buoc tiep theo thanh cong; khong co loi</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Quiz doc duoc tao trong Firestore voi duration = 5</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Xoa quiz doc via Firestore REST API</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>BVA: bien duoi = 5 (valid) | Run: 2026-04-18 12:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="55" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>TC-CQ-008</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Create Quiz - Duration</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Duration = 6 (bien duoi + 1) phai duoc chap nhan</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>CREATOR</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 6</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Chuyen sang buoc tiep theo thanh cong; khong co loi</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Quiz doc duoc tao trong Firestore voi duration = 6</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Xoa quiz doc via Firestore REST API</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>BVA: bien duoi + 1 = 6 (valid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="55" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>TC-CQ-009</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Create Quiz - Duration</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Duration = 119 (bien tren - 1) phai duoc chap nhan</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>CREATOR</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 119</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Chuyen sang buoc tiep theo thanh cong; khong co loi</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Quiz doc duoc tao trong Firestore voi duration = 119</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Xoa quiz doc via Firestore REST API</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>BVA: bien tren - 1 = 119 (valid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="55" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>TC-CQ-010</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Create Quiz - Duration</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Duration = 120 (bien tren) phai duoc chap nhan</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>CREATOR</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 120</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Chuyen sang buoc tiep theo thanh cong; khong co loi</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Quiz doc duoc tao trong Firestore voi duration = 120</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Xoa quiz doc via Firestore REST API</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>BVA: bien tren = 120 (valid) | Run: 2026-04-18 12:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="55" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>TC-CQ-011</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Create Quiz - Duration</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Duration = 121 (bien tren + 1) phai bi tu choi</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>CREATOR</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 121</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Hien thi loi hoac button Next bi disabled; khong chuyen buoc</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Khong co document nao duoc tao trong Firestore</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
+  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
+	chromedriver!(No symbol) [0x7ff7c90ed7cd]
+	chromedriver!(No symbol) [0x7ff7c9146c4e]
+	chromedriver!(No symbol) [0x7ff7c9146f5c]
+	chromedriver!(No symbol) [0x7ff7c9197cc7]
+	chromedriver!(No symbol) [0x7ff7c9194818]
+	chromedriver!(No symbol) [0x7ff7c9139018]
+	chromedriver!(No symbol) [0x7ff7c9139f03]
+	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
+	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
+	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
+	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
+	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
+	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
+	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
+	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
+</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>BVA: bien tren + 1 = 121 (invalid) | Run: 2026-04-18 12:22</t>
         </is>
       </c>
     </row>

--- a/data/TC_QuizManagement.xlsx
+++ b/data/TC_QuizManagement.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC_QuizCRUD" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TC_QuizCRUD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>quizzes/yY3YTi0yYJPy1IGnyJQf EXISTS (status=draft)</t>
+          <t>quizzes/SDbRehDyPxb6o2r4KqPa EXISTS (status=draft)</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:20 | Run: 2026-04-19 01:45 | Run: 2026-04-19 01:49 | Run: 2026-04-19 01:49 | Run: 2026-04-19 02:05 | Run: 2026-04-19 02:07 | Run: 2026-04-19 02:11 | Run: 2026-04-19 02:13 | Run: 2026-04-19 02:26 | Run: 2026-04-19 02:27 | Run: 2026-04-19 02:42 | Run: 2026-04-19 02:42 | Run: 2026-04-19 09:25 | Run: 2026-04-19 09:27 | Run: 2026-04-19 09:33 | Run: 2026-04-19 09:43 | Run: 2026-04-19 09:44 | Run: 2026-04-19 09:45 | Run: 2026-04-19 09:48 | Run: 2026-04-19 09:52 | Run: 2026-04-19 09:55 | Run: 2026-04-19 09:58 | Run: 2026-04-19 10:03 | Run: 2026-04-19 10:06 | Run: 2026-04-19 10:08 | Run: 2026-04-19 10:12 | Run: 2026-04-19 10:18 | Run: 2026-04-19 10:35 | Run: 2026-04-19 10:39 | Run: 2026-04-19 10:43 | Run: 2026-04-19 10:51</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:20 | Run: 2026-04-19 01:45 | Run: 2026-04-19 01:49 | Run: 2026-04-19 01:49 | Run: 2026-04-19 02:05 | Run: 2026-04-19 02:07 | Run: 2026-04-19 02:11 | Run: 2026-04-19 02:13 | Run: 2026-04-19 02:26 | Run: 2026-04-19 02:27 | Run: 2026-04-19 02:42 | Run: 2026-04-19 02:42 | Run: 2026-04-19 09:25 | Run: 2026-04-19 09:27 | Run: 2026-04-19 09:33 | Run: 2026-04-19 09:43 | Run: 2026-04-19 09:44 | Run: 2026-04-19 09:45 | Run: 2026-04-19 09:48 | Run: 2026-04-19 09:52 | Run: 2026-04-19 09:55 | Run: 2026-04-19 09:58 | Run: 2026-04-19 10:03 | Run: 2026-04-19 10:06 | Run: 2026-04-19 10:08 | Run: 2026-04-19 10:12 | Run: 2026-04-19 10:18 | Run: 2026-04-19 10:35 | Run: 2026-04-19 10:39 | Run: 2026-04-19 10:43 | Run: 2026-04-19 10:51 | Run: 2026-04-19 18:48 | Run: 2026-04-19 18:53 | Run: 2026-04-19 18:58 | Run: 2026-04-19 19:04 | Run: 2026-04-19 19:09 | Run: 2026-04-19 19:35 | Run: 2026-04-19 22:05</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       <c r="J7" s="8" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:21 | Run: 2026-04-19 01:40 | Run: 2026-04-19 01:40 | Run: 2026-04-19 01:43 | Run: 2026-04-19 01:46 | Run: 2026-04-19 02:12 | Run: 2026-04-19 10:59 | Run: 2026-04-19 11:01</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:21 | Run: 2026-04-19 01:40 | Run: 2026-04-19 01:40 | Run: 2026-04-19 01:43 | Run: 2026-04-19 01:46 | Run: 2026-04-19 02:12 | Run: 2026-04-19 10:59 | Run: 2026-04-19 11:01 | Run: 2026-04-19 19:32 | Run: 2026-04-19 19:36</t>
         </is>
       </c>
     </row>
@@ -919,91 +919,69 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
+          <t>Continue disabled with 0 questions – validation ✓</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:21 | Run: 2026-04-19 01:46 | Run: 2026-04-19 02:12 | Run: 2026-04-19 19:38 | Run: 2026-04-19 22:34 | Run: 2026-04-19 22:41 | Run: 2026-04-19 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>TC-CQ-004</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Create Quiz</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Create with XSS in title</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>CREATOR</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Title='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Script not executed; title stored as escaped text</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Firestore stores escaped string</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Delete quiz doc</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">EXCEPTION: Message: 
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7a3e00245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7a3e002b0+14740]
+	chromedriver!GetHandleVerifier [0x7ff71a6e0245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff71a6e02b0+14740]
 	chromedriver!(No </t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:21 | Run: 2026-04-19 01:46 | Run: 2026-04-19 02:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>TC-CQ-004</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Create Quiz</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Create with XSS in title</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>CREATOR</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Title='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Script not executed; title stored as escaped text</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Firestore stores escaped string</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Delete quiz doc</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr"/>
@@ -1014,7 +992,7 @@
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:21</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:21 | Run: 2026-04-19 19:41 | Run: 2026-04-19 22:53</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1039,12 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Quiz 'TC-RQ-001_Auto_1776538007': FOUND in /creator/my</t>
+          <t>Quiz 'TC-RQ-001_Auto_1776614200': FOUND in /creator/my</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>quizzes/ZT2XFN1up486obDC2Isr status=draft</t>
+          <t>quizzes/p63KyRPWdOiwlvyZhnYg status=draft</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1076,7 +1054,7 @@
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 01:40 | Run: 2026-04-19 01:43 | Run: 2026-04-19 01:47</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 01:40 | Run: 2026-04-19 01:43 | Run: 2026-04-19 01:47 | Run: 2026-04-19 22:30 | Run: 2026-04-19 22:57</t>
         </is>
       </c>
     </row>
@@ -1123,32 +1101,14 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr"/>
+          <t>Quiz 'TC-RQ-002_Auto_1776615125' not visible in admin quiz-management</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>quizzes/IHhKms5X5rNLPFFu3JcL status=pending</t>
+        </is>
+      </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
           <t>FAIL</t>
@@ -1156,7 +1116,7 @@
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 22:59 | Run: 2026-04-19 23:04 | Run: 2026-04-19 23:08 | Run: 2026-04-19 23:13</t>
         </is>
       </c>
     </row>
@@ -1203,22 +1163,22 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>TC-CQ-001 chưa tạo quiz – skip</t>
+          <t>URL after /edit: https://datn-quizapp.web.app/quiz/MAKMl4DKaOZLOEjVyiah/edit</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>quizzes/MAKMl4DKaOZLOEjVyiah status=draft</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>Bug: edit not persisted | Run: 2026-04-18 12:22</t>
+          <t>Bug: edit not persisted | Run: 2026-04-18 12:22 | Run: 2026-04-19 23:14</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1225,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Không có quiz ID để test</t>
+          <t>Regular user blocked from edit page ✓</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1275,12 +1235,12 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 23:15</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1287,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Không có quiz ID để test</t>
+          <t>EXCEPTION: 403 Client Error: Forbidden for url: https://firestore.googleapis.com/v1/projects/datn-quizapp/databases/(default)/documents/quizzes</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -1337,12 +1297,12 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 23:16</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1364,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>Bug: delete partially works | Run: 2026-04-18 12:22 | Run: 2026-04-19 01:47</t>
+          <t>Bug: delete partially works | Run: 2026-04-18 12:22 | Run: 2026-04-19 01:47 | Run: 2026-04-19 23:18</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1426,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 01:44 | Run: 2026-04-19 01:48</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 01:44 | Run: 2026-04-19 01:48 | Run: 2026-04-19 23:20</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1473,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>File not found: C:\quiz-trivia-tooltest\data\sample_import_valid.csv</t>
+          <t>Import result: Chỉ chấp nhận: jpeg, png, webp</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1523,12 +1483,12 @@
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>Known: import fails for most formats | Run: 2026-04-18 12:22</t>
+          <t>Known: import fails for most formats | Run: 2026-04-18 12:22 | Run: 2026-04-19 23:28 | Run: 2026-04-19 23:35 | Run: 2026-04-19 23:40</t>
         </is>
       </c>
     </row>
@@ -1575,29 +1535,11 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+          <t xml:space="preserve">EXCEPTION: Message: 
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
+	chromedriver!GetHandleVerifier [0x7ff71a6e0245+146d5]
+	chromedriver!GetHandleVerifier [0x7ff71a6e02b0+14740]
+	chromedriver!(No </t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr"/>
@@ -1608,7 +1550,7 @@
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 23:30</t>
         </is>
       </c>
     </row>
@@ -1655,29 +1597,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
+          <t>Bad schema result: Chỉ chấp nhận: jpeg, png, webp</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr"/>
@@ -1688,7 +1608,7 @@
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:22</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 23:42</t>
         </is>
       </c>
     </row>
@@ -1735,29 +1655,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
+          <t>No clear size-validation response</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr"/>
@@ -1768,7 +1666,7 @@
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Run: 2026-04-18 12:23</t>
+          <t xml:space="preserve"> | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:45</t>
         </is>
       </c>
     </row>
@@ -1815,22 +1713,22 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Không có quiz ID</t>
+          <t>Draft quiz inaccessible to regular user ✓</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>quizzes/Fibt8mu2iWJNAkteCU8X status=draft</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>Verified in system test | Run: 2026-04-18 12:23</t>
+          <t>Verified in system test | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:46</t>
         </is>
       </c>
     </row>
@@ -1877,22 +1775,22 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>Không có quiz ID</t>
+          <t>Submit result: No toast</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Firestore status: draft</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>Bug: state transition unreliable | Run: 2026-04-18 12:23</t>
+          <t>Bug: state transition unreliable | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:49</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1837,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Không có quiz ID</t>
+          <t>Quiz not found in any admin route</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -1949,12 +1847,12 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>Bug: approval flow broken | Run: 2026-04-18 12:23</t>
+          <t>Bug: approval flow broken | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:50</t>
         </is>
       </c>
     </row>
@@ -2001,7 +1899,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>Không có quiz ID</t>
+          <t>EXCEPTION: 403 Client Error: Forbidden for url: https://firestore.googleapis.com/v1/projects/datn-quizapp/databases/(default)/documents/quizzes</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
@@ -2011,12 +1909,12 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>Bug: client-side only check | Run: 2026-04-18 12:23</t>
+          <t>Bug: client-side only check | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:51</t>
         </is>
       </c>
     </row>
@@ -2063,7 +1961,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Không có quiz ID</t>
+          <t>EXCEPTION: 403 Client Error: Forbidden for url: https://firestore.googleapis.com/v1/projects/datn-quizapp/databases/(default)/documents/quizzes</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -2073,12 +1971,12 @@
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>Verified in system test | Run: 2026-04-18 12:23</t>
+          <t>Verified in system test | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:51</t>
         </is>
       </c>
     </row>
@@ -2125,40 +2023,18 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
+          <t>dur=-1: validation blocked as expected ✓</t>
         </is>
       </c>
       <c r="J26" s="11" t="n"/>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>BVA: gia tri am – ngoai vung hop le | Run: 2026-04-18 12:21</t>
+          <t>BVA: gia tri am – ngoai vung hop le | Run: 2026-04-18 12:21 | Run: 2026-04-19 19:42 | Run: 2026-04-19 22:26</t>
         </is>
       </c>
     </row>
@@ -2205,40 +2081,18 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
+          <t>dur=4: validation blocked as expected ✓</t>
         </is>
       </c>
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>BVA: bien duoi - 1 = 4 (invalid) | Run: 2026-04-18 12:21</t>
+          <t>BVA: bien duoi - 1 = 4 (invalid) | Run: 2026-04-18 12:21 | Run: 2026-04-19 19:44 | Run: 2026-04-19 22:28</t>
         </is>
       </c>
     </row>
@@ -2285,29 +2139,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
+          <t>dur=5: did not advance to Questions step</t>
         </is>
       </c>
       <c r="J28" s="11" t="n"/>
@@ -2318,7 +2150,7 @@
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>BVA: bien duoi = 5 (valid) | Run: 2026-04-18 12:21</t>
+          <t>BVA: bien duoi = 5 (valid) | Run: 2026-04-18 12:21 | Run: 2026-04-19 19:47</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2167,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Duration = 6 (bien duoi + 1) phai duoc chap nhan</t>
+          <t>Duration = 120 (bien tren) phai duoc chap nhan</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -2345,7 +2177,7 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 6</t>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 120</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2355,7 +2187,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Quiz doc duoc tao trong Firestore voi duration = 6</t>
+          <t>Quiz doc duoc tao trong Firestore voi duration = 120</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -2363,16 +2195,20 @@
           <t>Xoa quiz doc via Firestore REST API</t>
         </is>
       </c>
-      <c r="I29" s="11" t="n"/>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>dur=120: did not advance to Questions step</t>
+        </is>
+      </c>
       <c r="J29" s="11" t="n"/>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>BVA: bien duoi + 1 = 6 (valid)</t>
+          <t>BVA: bien tren = 120 (valid) | Run: 2026-04-18 12:22 | Run: 2026-04-19 21:42 | Run: 2026-04-19 22:08</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2225,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Duration = 119 (bien tren - 1) phai duoc chap nhan</t>
+          <t>Duration = 121 (bien tren + 1) phai bi tu choi</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -2399,197 +2235,43 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 119</t>
+          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 121</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Chuyen sang buoc tiep theo thanh cong; khong co loi</t>
+          <t>Hien thi loi hoac button Next bi disabled; khong chuyen buoc</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>Quiz doc duoc tao trong Firestore voi duration = 119</t>
+          <t>Khong co document nao duoc tao trong Firestore</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Xoa quiz doc via Firestore REST API</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="n"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>dur=121: validation blocked as expected ✓</t>
+        </is>
+      </c>
       <c r="J30" s="11" t="n"/>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>BVA: bien tren - 1 = 119 (valid)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="55" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>TC-CQ-010</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Create Quiz - Duration</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Duration = 120 (bien tren) phai duoc chap nhan</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>CREATOR</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 120</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Chuyen sang buoc tiep theo thanh cong; khong co loi</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>Quiz doc duoc tao trong Firestore voi duration = 120</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>Xoa quiz doc via Firestore REST API</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>BVA: bien tren = 120 (valid) | Run: 2026-04-18 12:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="55" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>TC-CQ-011</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Create Quiz - Duration</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Duration = 121 (bien tren + 1) phai bi tu choi</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>CREATOR</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Title='Test Quiz BVA'; thong tin hop le; Duration = 121</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>Hien thi loi hoac button Next bi disabled; khong chuyen buoc</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>Khong co document nao duoc tao trong Firestore</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lỗi script: Message: no such element: Unable to locate element: {"method":"css selector","selector":"button[type='submit'], button.btn-login, button.login-btn"}
-  (Session info: chrome=147.0.7727.57); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff7c9380245+146d5]
-	chromedriver!GetHandleVerifier [0x7ff7c93802b0+14740]
-	chromedriver!(No symbol) [0x7ff7c90ed7cd]
-	chromedriver!(No symbol) [0x7ff7c9146c4e]
-	chromedriver!(No symbol) [0x7ff7c9146f5c]
-	chromedriver!(No symbol) [0x7ff7c9197cc7]
-	chromedriver!(No symbol) [0x7ff7c9194818]
-	chromedriver!(No symbol) [0x7ff7c9139018]
-	chromedriver!(No symbol) [0x7ff7c9139f03]
-	chromedriver!GetHandleVerifier [0x7ff7c96958f9+329d89]
-	chromedriver!GetHandleVerifier [0x7ff7c968fe46+3242d6]
-	chromedriver!GetHandleVerifier [0x7ff7c96b30b2+347542]
-	chromedriver!GetHandleVerifier [0x7ff7c939d3d5+31865]
-	chromedriver!GetHandleVerifier [0x7ff7c93a600c+3a49c]
-	chromedriver!GetHandleVerifier [0x7ff7c9389634+1dac4]
-	chromedriver!GetHandleVerifier [0x7ff7c93897e6+1dc76]
-	chromedriver!GetHandleVerifier [0x7ff7c936e2f7+2787]
-	KERNEL32!BaseThreadInitThunk [0x7ffc6910e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc6a7ec3fc+2c]
-</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>BVA: bien tren + 1 = 121 (invalid) | Run: 2026-04-18 12:22</t>
-        </is>
-      </c>
-    </row>
+          <t>BVA: bien tren + 1 = 121 (invalid) | Run: 2026-04-18 12:22 | Run: 2026-04-19 22:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="55" customHeight="1"/>
+    <row r="32" ht="55" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:L2"/>

--- a/data/TC_QuizManagement.xlsx
+++ b/data/TC_QuizManagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\quiz-trivia-tooltest\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC77EB9-E85F-41F6-802B-EC879F6531FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEABBB3-7FA5-484F-AEBB-6CCEAA989D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5370" yWindow="3390" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC_QuizCRUD" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="190">
   <si>
     <t>Project</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>TC-CQ-001</t>
-  </si>
-  <si>
     <t>Create Quiz</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>TC-CQ-002</t>
-  </si>
-  <si>
     <t>Create with empty title</t>
   </si>
   <si>
@@ -136,9 +130,6 @@
     <t>Continue button disabled when title empty ✓</t>
   </si>
   <si>
-    <t>TC-CQ-003</t>
-  </si>
-  <si>
     <t>Create with no questions</t>
   </si>
   <si>
@@ -152,24 +143,6 @@
   </si>
   <si>
     <t>Continue disabled with 0 questions – validation ✓</t>
-  </si>
-  <si>
-    <t>TC-CQ-004</t>
-  </si>
-  <si>
-    <t>Create with XSS in title</t>
-  </si>
-  <si>
-    <t>Title='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
-  </si>
-  <si>
-    <t>Script not executed; title stored as escaped text</t>
-  </si>
-  <si>
-    <t>Firestore stores escaped string</t>
-  </si>
-  <si>
-    <t>Delete quiz doc</t>
   </si>
   <si>
     <t xml:space="preserve">EXCEPTION: Message: 
@@ -182,12 +155,6 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t xml:space="preserve"> | Run: 2026-04-18 12:21 | Run: 2026-04-19 19:41 | Run: 2026-04-19 22:53</t>
-  </si>
-  <si>
-    <t>TC-RQ-001</t>
-  </si>
-  <si>
     <t>Read Quiz</t>
   </si>
   <si>
@@ -212,9 +179,6 @@
     <t>quizzes/p63KyRPWdOiwlvyZhnYg status=draft</t>
   </si>
   <si>
-    <t>TC-RQ-002</t>
-  </si>
-  <si>
     <t>Admin views all quizzes</t>
   </si>
   <si>
@@ -239,9 +203,6 @@
     <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 22:59 | Run: 2026-04-19 23:04 | Run: 2026-04-19 23:08 | Run: 2026-04-19 23:13</t>
   </si>
   <si>
-    <t>TC-UQ-001</t>
-  </si>
-  <si>
     <t>Update Quiz</t>
   </si>
   <si>
@@ -269,9 +230,6 @@
     <t>Bug: edit not persisted | Run: 2026-04-18 12:22 | Run: 2026-04-19 23:14</t>
   </si>
   <si>
-    <t>TC-UQ-002</t>
-  </si>
-  <si>
     <t>User cannot edit any quiz</t>
   </si>
   <si>
@@ -290,9 +248,6 @@
     <t>Regular user blocked from edit page ✓</t>
   </si>
   <si>
-    <t>TC-UQ-003</t>
-  </si>
-  <si>
     <t>Creator cannot edit another creator's quiz</t>
   </si>
   <si>
@@ -308,9 +263,6 @@
     <t xml:space="preserve"> | Run: 2026-04-18 12:22 | Run: 2026-04-19 23:16</t>
   </si>
   <si>
-    <t>TC-DQ-001</t>
-  </si>
-  <si>
     <t>Delete Quiz</t>
   </si>
   <si>
@@ -338,9 +290,6 @@
     <t>Bug: delete partially works | Run: 2026-04-18 12:22 | Run: 2026-04-19 01:47 | Run: 2026-04-19 23:18</t>
   </si>
   <si>
-    <t>TC-DQ-002</t>
-  </si>
-  <si>
     <t>User cannot delete quiz</t>
   </si>
   <si>
@@ -356,9 +305,6 @@
     <t>User has no delete capability for creator quizzes ✓</t>
   </si>
   <si>
-    <t>TC-IMP-001</t>
-  </si>
-  <si>
     <t>Import Quiz</t>
   </si>
   <si>
@@ -425,24 +371,6 @@
     <t>TC-IMP-004</t>
   </si>
   <si>
-    <t>Import oversized file (&gt;5MB)</t>
-  </si>
-  <si>
-    <t>Upload data/sample_import_large.csv</t>
-  </si>
-  <si>
-    <t>Error: file too large</t>
-  </si>
-  <si>
-    <t>No clear size-validation response</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:45</t>
-  </si>
-  <si>
-    <t>TC-QST-001</t>
-  </si>
-  <si>
     <t>State Transition</t>
   </si>
   <si>
@@ -464,9 +392,6 @@
     <t>quizzes/Fibt8mu2iWJNAkteCU8X status=draft</t>
   </si>
   <si>
-    <t>TC-QST-002</t>
-  </si>
-  <si>
     <t>Submit quiz for review (draft→pending)</t>
   </si>
   <si>
@@ -491,9 +416,6 @@
     <t>Bug: state transition unreliable | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:49</t>
   </si>
   <si>
-    <t>TC-QST-003</t>
-  </si>
-  <si>
     <t>Admin approves quiz (pending→published)</t>
   </si>
   <si>
@@ -551,9 +473,6 @@
     <t>Verified in system test | Run: 2026-04-18 12:23 | Run: 2026-04-19 23:51</t>
   </si>
   <si>
-    <t>TC-CQ-005</t>
-  </si>
-  <si>
     <t>Create Quiz - Duration</t>
   </si>
   <si>
@@ -572,9 +491,6 @@
     <t>dur=-1: validation blocked as expected ✓</t>
   </si>
   <si>
-    <t>TC-CQ-006</t>
-  </si>
-  <si>
     <t>Duration = 4 (bien duoi - 1) phai bi tu choi</t>
   </si>
   <si>
@@ -587,9 +503,6 @@
     <t>dur=4: validation blocked as expected ✓</t>
   </si>
   <si>
-    <t>TC-CQ-007</t>
-  </si>
-  <si>
     <t>Duration = 5 (bien duoi) phai duoc chap nhan</t>
   </si>
   <si>
@@ -608,9 +521,6 @@
     <t>dur=5: advanced to Questions step ✓</t>
   </si>
   <si>
-    <t>TC-CQ-008</t>
-  </si>
-  <si>
     <t>Duration = 120 (bien tren) phai duoc chap nhan</t>
   </si>
   <si>
@@ -623,9 +533,6 @@
     <t>dur=120: advanced to Questions step ✓</t>
   </si>
   <si>
-    <t>TC-CQ-009</t>
-  </si>
-  <si>
     <t>Duration = 121 (bien tren + 1) phai bi tu choi</t>
   </si>
   <si>
@@ -633,13 +540,67 @@
   </si>
   <si>
     <t>dur=121: validation blocked as expected ✓</t>
+  </si>
+  <si>
+    <t>TC-CR-025</t>
+  </si>
+  <si>
+    <t>TC-CR-005</t>
+  </si>
+  <si>
+    <t>TC-CR-027</t>
+  </si>
+  <si>
+    <t>TC-CR-010</t>
+  </si>
+  <si>
+    <t>TC-CR-011</t>
+  </si>
+  <si>
+    <t>TC-CR-012</t>
+  </si>
+  <si>
+    <t>TC-CR-013</t>
+  </si>
+  <si>
+    <t>TC-CR-014</t>
+  </si>
+  <si>
+    <t>TC-RD-001</t>
+  </si>
+  <si>
+    <t>TC-RD-002</t>
+  </si>
+  <si>
+    <t>TC-UP-001</t>
+  </si>
+  <si>
+    <t>TC-UP-014</t>
+  </si>
+  <si>
+    <t>TC-UP-011</t>
+  </si>
+  <si>
+    <t>TC-DL-001</t>
+  </si>
+  <si>
+    <t>TC-DL-011</t>
+  </si>
+  <si>
+    <t>TC-QM-008</t>
+  </si>
+  <si>
+    <t>TC-ST-002</t>
+  </si>
+  <si>
+    <t>TC-ST-003</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,8 +641,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -723,8 +690,20 @@
         <fgColor rgb="FFD6EAF8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -786,11 +765,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -814,6 +823,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1116,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1205,7 +1223,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="10"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1243,912 +1261,840 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:12" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:12" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:12" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="7"/>
+    </row>
+    <row r="10" spans="1:12" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="7"/>
+    </row>
+    <row r="11" spans="1:12" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="7"/>
+    </row>
+    <row r="12" spans="1:12" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="1:12" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="7"/>
+    </row>
+    <row r="14" spans="1:12" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="D14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="5" t="s">
+      <c r="K14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" ht="50.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="G15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="H15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="J15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="K15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="3" t="s">
+    </row>
+    <row r="16" spans="1:12" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="K10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" ht="50" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="K16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="4" t="s">
+    </row>
+    <row r="17" spans="1:12" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="G17" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="H17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="J17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="1:12" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J12" s="3" t="s">
+    </row>
+    <row r="19" spans="1:12" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="D19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="J19" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="4" t="s">
+      <c r="K19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="4"/>
-    </row>
-    <row r="14" spans="1:12" ht="75" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+    </row>
+    <row r="20" spans="1:12" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="J20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:12" ht="63" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="D21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="J21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" s="4" t="s">
+    </row>
+    <row r="22" spans="1:12" ht="88" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L15" s="4" t="s">
+      <c r="D22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" s="3" t="s">
+    </row>
+    <row r="23" spans="1:12" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="D23" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="1:12" ht="62.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="H23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="J23" s="4"/>
+      <c r="K23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G17" s="4" t="s">
+    </row>
+    <row r="24" spans="1:12" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="D24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L17" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="G24" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="H24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="J24" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="K24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" s="4"/>
+    </row>
+    <row r="25" spans="1:12" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L18" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+      <c r="G25" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="I25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="J25" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="K25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="4" t="s">
+    </row>
+    <row r="26" spans="1:12" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J19" s="4"/>
-      <c r="K19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L19" s="4" t="s">
+      <c r="D26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="G26" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="H26" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="I26" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L26" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L20" s="3" t="s">
+    </row>
+    <row r="27" spans="1:12" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="13" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I21" s="4" t="s">
+    </row>
+    <row r="28" spans="1:12" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="B28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="K21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" s="4"/>
-    </row>
-    <row r="22" spans="1:12" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="F28" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="G28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L28" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="75" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="75" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" s="7"/>
-    </row>
-    <row r="27" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="7"/>
-    </row>
-    <row r="28" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="7"/>
-    </row>
-    <row r="29" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="7"/>
-    </row>
-    <row r="30" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="J30" s="7"/>
-      <c r="K30" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L30" s="7"/>
-    </row>
-    <row r="31" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35"/>
+    </row>
+    <row r="29" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:12" ht="55" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:L2"/>
